--- a/data/fmsForecastOutput/File1/RPT_RPT2772174638977HO_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT2772174638977HO_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>408.7333657886404</v>
+        <v>428.1491961764174</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>438.7252650738636</v>
+        <v>457.6440469708218</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>468.9540363164136</v>
+        <v>488.8331072009524</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>528.9829036753313</v>
+        <v>548.3251848004669</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>564.8457039941433</v>
+        <v>579.8981852741933</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>408.7333657886404</v>
+        <v>428.1491961764174</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>438.7252650738636</v>
+        <v>457.6440469708218</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>468.9540363164136</v>
+        <v>488.8331072009524</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>528.9829036753313</v>
+        <v>548.3251848004669</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>564.8457039941433</v>
+        <v>579.8981852741933</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>5653846.894268111</v>
+        <v>5922418.392280669</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>6700023.824717863</v>
+        <v>6988943.336619966</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>7819019.014773173</v>
+        <v>8150469.052954222</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>9026386.940271595</v>
+        <v>9356437.141383847</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>10565110.98315269</v>
+        <v>10846658.90707424</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>407.6883366639186</v>
+        <v>427.0545256229938</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>437.6035541539125</v>
+        <v>456.4739654510093</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>467.7550379788033</v>
+        <v>487.5832830443961</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>527.6304265176273</v>
+        <v>546.923254261155</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>563.4015346136747</v>
+        <v>578.4155304588334</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>407.6883366639186</v>
+        <v>427.0545256229938</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>437.6035541539125</v>
+        <v>456.4739654510093</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>467.7550379788033</v>
+        <v>487.5832830443961</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>527.6304265176273</v>
+        <v>546.923254261155</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>563.4015346136747</v>
+        <v>578.4155304588334</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>5653846.894268111</v>
+        <v>5922418.392280669</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>6700023.824717863</v>
+        <v>6988943.336619966</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>7819019.014773173</v>
+        <v>8150469.052954222</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>9026386.940271595</v>
+        <v>9356437.141383847</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>10565110.98315269</v>
+        <v>10846658.90707424</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>811.3066839943605</v>
+        <v>833.7244697813006</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>889.2369166108344</v>
+        <v>910.4986582981267</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>959.7244895281032</v>
+        <v>979.8352956975715</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1217.459514609757</v>
+        <v>1240.309599904299</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1296.757453016447</v>
+        <v>1316.691010341154</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>811.3066839943605</v>
+        <v>833.7244697813006</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>889.2369166108344</v>
+        <v>910.4986582981267</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>959.7244895281032</v>
+        <v>979.8352956975715</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>1217.459514609757</v>
+        <v>1240.309599904299</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>1296.757453016447</v>
+        <v>1316.691010341154</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>2309875.290968732</v>
+        <v>2373701.080265254</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>2719454.98440542</v>
+        <v>2784477.419179067</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>3159722.739748795</v>
+        <v>3225934.00377478</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>3533805.388202055</v>
+        <v>3600130.184686652</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>4137231.277461365</v>
+        <v>4200828.16417523</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>1002.845467133535</v>
+        <v>1030.55579579608</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1099.173997483269</v>
+        <v>1125.455355316398</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1186.302754565984</v>
+        <v>1211.161456220157</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1504.885611978362</v>
+        <v>1533.130300347532</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1602.904745375193</v>
+        <v>1627.544352075472</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>1002.845467133535</v>
+        <v>1030.55579579608</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>1099.173997483269</v>
+        <v>1125.455355316398</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>1186.302754565984</v>
+        <v>1211.161456220157</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>1504.885611978362</v>
+        <v>1533.130300347532</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>1602.904745375193</v>
+        <v>1627.544352075472</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>2309875.290968732</v>
+        <v>2373701.080265254</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>2719454.98440542</v>
+        <v>2784477.419179067</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>3159722.739748795</v>
+        <v>3225934.00377478</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>3533805.388202055</v>
+        <v>3600130.184686652</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>4137231.277461365</v>
+        <v>4200828.16417523</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>477.4497012577662</v>
+        <v>497.3779435838001</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>513.8899150007749</v>
+        <v>533.1996029971257</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>549.8818095026066</v>
+        <v>569.7990934059922</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>629.0705169702812</v>
+        <v>648.9227467874216</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>671.4973433596716</v>
+        <v>687.2610780971581</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>477.4497012577662</v>
+        <v>497.3779435838001</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>513.8899150007749</v>
+        <v>533.1996029971257</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>549.8818095026066</v>
+        <v>569.7990934059922</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>629.0705169702812</v>
+        <v>648.9227467874216</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>671.4973433596716</v>
+        <v>687.2610780971581</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>7963722.185236843</v>
+        <v>8296119.472545923</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>9419478.809123283</v>
+        <v>9773420.755799031</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>10978741.75452197</v>
+        <v>11376403.056729</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>12560192.32847365</v>
+        <v>12956567.3260705</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>14702342.26061405</v>
+        <v>15047487.07124946</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>492.4577161038538</v>
+        <v>513.0123769948121</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>529.6363031743601</v>
+        <v>549.5376701156091</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>566.5114141868005</v>
+        <v>587.0310394514975</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>645.5815037791497</v>
+        <v>665.9547879070469</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>689.1685807488751</v>
+        <v>705.347156589519</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>492.4577161038538</v>
+        <v>513.0123769948121</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>529.6363031743601</v>
+        <v>549.5376701156091</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>566.5114141868005</v>
+        <v>587.0310394514975</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>645.5815037791497</v>
+        <v>665.9547879070469</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>689.1685807488751</v>
+        <v>705.347156589519</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>7963722.185236843</v>
+        <v>8296119.472545923</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>9419478.809123283</v>
+        <v>9773420.755799031</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>10978741.75452197</v>
+        <v>11376403.056729</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>12560192.32847365</v>
+        <v>12956567.3260705</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>14702342.26061405</v>
+        <v>15047487.07124946</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>1116.864176966724</v>
+        <v>1125.685637008789</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>1220.549827190541</v>
+        <v>1229.169584201536</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1299.70750744539</v>
+        <v>1308.046275033991</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1402.875125635811</v>
+        <v>1411.101304321292</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>1481.236914075989</v>
+        <v>1489.126842460039</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>1116.864176966724</v>
+        <v>1125.685637008789</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>1220.549827190541</v>
+        <v>1229.169584201536</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>1299.70750744539</v>
+        <v>1308.046275033991</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>1402.875125635811</v>
+        <v>1411.101304321292</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>1481.236914075989</v>
+        <v>1489.126842460039</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>88486.56353944131</v>
+        <v>89185.46739957119</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>106408.2226361601</v>
+        <v>107159.6979161221</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>127998.7265520749</v>
+        <v>128819.9510400773</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>152194.776774921</v>
+        <v>153087.2164553095</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>184313.2190974131</v>
+        <v>185294.9783859462</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1146.285022564316</v>
+        <v>1155.3388607408</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1252.701998198001</v>
+        <v>1261.548820008225</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1333.94487908572</v>
+        <v>1342.503309547174</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1439.830176496273</v>
+        <v>1448.273052196445</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1520.256199895362</v>
+        <v>1528.353967665391</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>1146.285022564316</v>
+        <v>1155.3388607408</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>1252.701998198001</v>
+        <v>1261.548820008225</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>1333.94487908572</v>
+        <v>1342.503309547174</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>1439.830176496273</v>
+        <v>1448.273052196445</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>1520.256199895362</v>
+        <v>1528.353967665391</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>88486.56353944131</v>
+        <v>89185.46739957119</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>106408.2226361601</v>
+        <v>107159.6979161221</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>127998.7265520749</v>
+        <v>128819.9510400773</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>152194.776774921</v>
+        <v>153087.2164553095</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>184313.2190974131</v>
+        <v>185294.9783859462</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>480.472525983425</v>
+        <v>500.3482611214205</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>517.2350422580162</v>
+        <v>536.4941271581673</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>553.5622532641053</v>
+        <v>573.4227051887319</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>633.2523020939333</v>
+        <v>653.0417025519246</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>676.0732158478486</v>
+        <v>691.7924553733275</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>480.472525983425</v>
+        <v>500.3482611214205</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>517.2350422580162</v>
+        <v>536.4941271581673</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>553.5622532641053</v>
+        <v>573.4227051887319</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>633.2523020939333</v>
+        <v>653.0417025519246</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>676.0732158478486</v>
+        <v>691.7924553733275</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>8052208.748776284</v>
+        <v>8385304.939945493</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>9525887.031759443</v>
+        <v>9880580.453715155</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>11106740.48107404</v>
+        <v>11505223.00776908</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>12712387.10524857</v>
+        <v>13109654.54252581</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>14886655.47971146</v>
+        <v>15232782.04963541</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>495.5639377064616</v>
+        <v>516.0639601575591</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>533.0733601315441</v>
+        <v>552.9221798402073</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>570.2925262922068</v>
+        <v>590.753219257839</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>649.8733742773424</v>
+        <v>670.1821902232693</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>693.8649727564572</v>
+        <v>709.9978847686872</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>495.5639377064616</v>
+        <v>516.0639601575591</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>533.0733601315441</v>
+        <v>552.9221798402073</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>570.2925262922068</v>
+        <v>590.753219257839</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>649.8733742773424</v>
+        <v>670.1821902232693</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>693.8649727564572</v>
+        <v>709.9978847686872</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>8052208.748776284</v>
+        <v>8385304.939945493</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>9525887.031759443</v>
+        <v>9880580.453715155</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>11106740.48107404</v>
+        <v>11505223.00776908</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>12712387.10524857</v>
+        <v>13109654.54252581</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>14886655.47971146</v>
+        <v>15232782.04963541</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>2376.235616754715</v>
+        <v>2376.892604768758</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>2446.52503057958</v>
+        <v>2447.078998650416</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>2560.317278211295</v>
+        <v>2560.801397512607</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>2674.357244279411</v>
+        <v>2674.773089479312</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>2824.018930082076</v>
+        <v>2824.377798604441</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>2376.235616754715</v>
+        <v>2376.892604768758</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>2446.52503057958</v>
+        <v>2447.078998650416</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>2560.317278211295</v>
+        <v>2560.801397512607</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>2674.357244279411</v>
+        <v>2674.773089479312</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>2824.018930082076</v>
+        <v>2824.377798604441</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>3032545.776071097</v>
+        <v>3033384.222483089</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>3546675.706107755</v>
+        <v>3547478.781929271</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>4175328.357466702</v>
+        <v>4176117.852215798</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>4921460.686222831</v>
+        <v>4922225.941428448</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>5899936.188174441</v>
+        <v>5900685.935762654</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>1263.665102547408</v>
+        <v>1264.0144840735</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>1301.044510002928</v>
+        <v>1301.339106260178</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>1361.558413278654</v>
+        <v>1361.815864459936</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>1422.204051446801</v>
+        <v>1422.425194949353</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>1501.79306534919</v>
+        <v>1501.983909062212</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>1263.665102547408</v>
+        <v>1264.0144840735</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>1301.044510002928</v>
+        <v>1301.339106260178</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>1361.558413278654</v>
+        <v>1361.815864459936</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>1422.204051446801</v>
+        <v>1422.425194949353</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>1501.79306534919</v>
+        <v>1501.983909062212</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>3032545.776071097</v>
+        <v>3033384.222483089</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>3546675.706107755</v>
+        <v>3547478.781929271</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>4175328.357466702</v>
+        <v>4176117.852215798</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>4921460.686222831</v>
+        <v>4922225.941428448</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>5899936.188174441</v>
+        <v>5900685.935762654</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>614.6200144808215</v>
+        <v>633.1357976969259</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>658.01646640863</v>
+        <v>675.9106279421152</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>704.4081175181863</v>
+        <v>722.8120689710053</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>804.6474311393008</v>
+        <v>822.8100004947362</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>862.2103149857604</v>
+        <v>876.5984524814002</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>614.6200144808215</v>
+        <v>633.1357976969259</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>658.01646640863</v>
+        <v>675.9106279421152</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>704.4081175181863</v>
+        <v>722.8120689710053</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>804.6474311393008</v>
+        <v>822.8100004947362</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>862.2103149857604</v>
+        <v>876.5984524814002</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>11084754.52484738</v>
+        <v>11418689.16242858</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>13072562.7378672</v>
+        <v>13428059.23564443</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>15282068.83854074</v>
+        <v>15681340.85998488</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>17633847.7914714</v>
+        <v>18031880.48395425</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>20786591.6678859</v>
+        <v>21133467.98539807</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>594.4084850984215</v>
+        <v>612.3153843086468</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>634.7207392329733</v>
+        <v>651.9813945756538</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>677.9347155403566</v>
+        <v>695.6470009083107</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>765.9638465032506</v>
+        <v>783.2532467392937</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>818.9087743936768</v>
+        <v>832.5743172868358</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>594.4084850984215</v>
+        <v>612.3153843086468</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>634.7207392329733</v>
+        <v>651.9813945756538</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>677.9347155403566</v>
+        <v>695.6470009083107</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>765.9638465032506</v>
+        <v>783.2532467392937</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>818.9087743936768</v>
+        <v>832.5743172868358</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>11084754.52484738</v>
+        <v>11418689.16242858</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>13072562.7378672</v>
+        <v>13428059.23564443</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>15282068.83854074</v>
+        <v>15681340.85998488</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>17633847.7914714</v>
+        <v>18031880.48395425</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>20786591.6678859</v>
+        <v>21133467.98539807</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>1449.67889630279</v>
       </c>
       <c r="E24" s="80" t="n">
-        <v>1630.78552529384</v>
+        <v>1630.785525293841</v>
       </c>
       <c r="F24" s="80" t="n">
         <v>1840.240564999343</v>
@@ -3876,7 +3876,7 @@
         <v>1449.67889630279</v>
       </c>
       <c r="O24" s="80" t="n">
-        <v>1630.78552529384</v>
+        <v>1630.785525293841</v>
       </c>
       <c r="P24" s="80" t="n">
         <v>1840.240564999343</v>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="T24" s="79" t="n">
-        <v>2399.801790805035</v>
+        <v>2399.801790805036</v>
       </c>
       <c r="U24" s="80" t="n">
         <v>2726.021806970903</v>
@@ -3920,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="79" t="n">
-        <v>2399.801790805035</v>
+        <v>2399.801790805036</v>
       </c>
       <c r="AE24" s="80" t="n">
         <v>2726.021806970903</v>
@@ -3948,7 +3948,7 @@
         <v>19866.6194619955</v>
       </c>
       <c r="E25" s="92" t="n">
-        <v>21694.90733920481</v>
+        <v>21694.90733920482</v>
       </c>
       <c r="F25" s="92" t="n">
         <v>21914.99917734606</v>
@@ -3978,7 +3978,7 @@
         <v>19866.6194619955</v>
       </c>
       <c r="O25" s="92" t="n">
-        <v>21694.90733920481</v>
+        <v>21694.90733920482</v>
       </c>
       <c r="P25" s="92" t="n">
         <v>21914.99917734606</v>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>418.1341945292034</v>
+        <v>438.2677603877486</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>459.1471193707464</v>
+        <v>479.2500286209769</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>493.7619694202501</v>
+        <v>515.0430396225207</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>566.4267270951323</v>
+        <v>587.297453416396</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>606.5304764977102</v>
+        <v>622.81173764866</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>418.1341945292034</v>
+        <v>438.2677603877486</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>459.1471193707464</v>
+        <v>479.2500286209769</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>493.7619694202501</v>
+        <v>515.0430396225207</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>566.4267270951323</v>
+        <v>587.297453416396</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>606.5304764977102</v>
+        <v>622.81173764866</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>5783884.837893843</v>
+        <v>6062384.486632435</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>7011897.612772891</v>
+        <v>7318900.609055791</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>8232649.53212571</v>
+        <v>8587475.548494624</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>9665315.791019045</v>
+        <v>10021446.86858571</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>11344800.45355755</v>
+        <v>11649331.99162031</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>417.0651298334892</v>
+        <v>437.1472191930065</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>457.973194870238</v>
+        <v>478.0247060027309</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>492.4995433941083</v>
+        <v>513.7262032153626</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>564.9785154334953</v>
+        <v>585.7958805205527</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>604.9797295657868</v>
+        <v>621.2193635986346</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>417.0651298334892</v>
+        <v>437.1472191930065</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>457.973194870238</v>
+        <v>478.0247060027309</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>492.4995433941083</v>
+        <v>513.7262032153626</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>564.9785154334953</v>
+        <v>585.7958805205527</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>604.9797295657868</v>
+        <v>621.2193635986346</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>5783884.837893843</v>
+        <v>6062384.486632435</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>7011897.612772891</v>
+        <v>7318900.609055791</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>8232649.53212571</v>
+        <v>8587475.548494624</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>9665315.791019045</v>
+        <v>10021446.86858571</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>11344800.45355755</v>
+        <v>11649331.99162031</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,49 +4510,49 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>824.8537073146637</v>
+        <v>848.2424265052473</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>923.3947374090013</v>
+        <v>946.173350012899</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>1001.336689817911</v>
+        <v>1023.085205904455</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>1303.99311274274</v>
+        <v>1328.638843946274</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>1392.447379179805</v>
+        <v>1414.005820488184</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>824.8537073146637</v>
+        <v>848.2424265052473</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>923.3947374090013</v>
+        <v>946.173350012899</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>1001.336689817911</v>
+        <v>1023.085205904455</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>1303.99311274274</v>
+        <v>1328.638843946274</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>1392.447379179805</v>
+        <v>1414.005820488184</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>2348445.088372205</v>
+        <v>2415035.226986311</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>2823916.072660772</v>
+        <v>2893577.386115463</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>3296723.532102585</v>
+        <v>3368326.665693805</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>3784978.336191924</v>
+        <v>3856515.185407929</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>4442524.572317785</v>
+        <v>4511305.55943829</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,49 +4560,49 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>1019.590763576838</v>
+        <v>1048.501250184512</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1141.39602822749</v>
+        <v>1169.552370148578</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1237.739045257725</v>
+        <v>1264.622098490925</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1611.848648712101</v>
+        <v>1642.312911252095</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1721.185798146517</v>
+        <v>1747.833902459095</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>1019.590763576838</v>
+        <v>1048.501250184512</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>1141.39602822749</v>
+        <v>1169.552370148578</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>1237.739045257725</v>
+        <v>1264.622098490925</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>1611.848648712101</v>
+        <v>1642.312911252095</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>1721.185798146517</v>
+        <v>1747.833902459095</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>2348445.088372205</v>
+        <v>2415035.226986311</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>2823916.072660772</v>
+        <v>2893577.386115463</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>3296723.532102585</v>
+        <v>3368326.665693805</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>3784978.336191924</v>
+        <v>3856515.185407929</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>4442524.572317785</v>
+        <v>4511305.55943829</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>487.5582552368809</v>
+        <v>508.2474520780377</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>536.603517158017</v>
+        <v>557.1528483935624</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>577.4607568647116</v>
+        <v>598.8189086317988</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>673.6507896320697</v>
+        <v>695.0703090754854</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>721.0515593852176</v>
+        <v>738.1017929099119</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>487.5582552368809</v>
+        <v>508.2474520780377</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>536.603517158017</v>
+        <v>557.1528483935624</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>577.4607568647116</v>
+        <v>598.8189086317988</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>673.6507896320697</v>
+        <v>695.0703090754854</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>721.0515593852176</v>
+        <v>738.1017929099119</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>8132329.926266048</v>
+        <v>8477419.713618746</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>9835813.685433663</v>
+        <v>10212477.99517125</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>11529373.06422829</v>
+        <v>11955802.21418843</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>13450294.12721097</v>
+        <v>13877962.05399364</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>15787325.02587533</v>
+        <v>16160637.5510586</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>502.8840194245042</v>
+        <v>524.2235544531762</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>553.0458855132484</v>
+        <v>574.2248802952015</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>594.9244080372824</v>
+        <v>616.9284760986237</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>691.3318587671607</v>
+        <v>713.3135686064732</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>740.026873884603</v>
+        <v>757.525804231609</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>502.8840194245042</v>
+        <v>524.2235544531762</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>553.0458855132484</v>
+        <v>574.2248802952015</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>594.9244080372824</v>
+        <v>616.9284760986237</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>691.3318587671607</v>
+        <v>713.3135686064732</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>740.026873884603</v>
+        <v>757.525804231609</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>8132329.926266048</v>
+        <v>8477419.713618746</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>9835813.685433663</v>
+        <v>10212477.99517125</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>11529373.06422829</v>
+        <v>11955802.21418843</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>13450294.12721097</v>
+        <v>13877962.05399364</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>15787325.02587533</v>
+        <v>16160637.5510586</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,49 +4714,49 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>1142.189996701186</v>
+        <v>1151.345916695978</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>1277.165793794042</v>
+        <v>1286.33279144933</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>1368.046684872855</v>
+        <v>1376.98223690925</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1497.942874649286</v>
+        <v>1506.855402817146</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1585.577104851201</v>
+        <v>1594.151956058279</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>1142.189996701186</v>
+        <v>1151.345916695978</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>1277.165793794042</v>
+        <v>1286.33279144933</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>1368.046684872855</v>
+        <v>1376.98223690925</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>1497.942874649286</v>
+        <v>1506.855402817146</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>1585.577104851201</v>
+        <v>1594.151956058279</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>90493.06961541572</v>
+        <v>91218.47196342688</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>111344.0345505115</v>
+        <v>112143.2185786265</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>134728.9544181315</v>
+        <v>135608.9518599762</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>162508.4636991528</v>
+        <v>163475.3638959133</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>197296.474011104</v>
+        <v>198363.4595920324</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4764,49 +4764,49 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1172.277984326794</v>
+        <v>1181.675092922694</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1310.809363349465</v>
+        <v>1320.217841417656</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>1404.084272178461</v>
+        <v>1413.255207802415</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1537.402235006568</v>
+        <v>1546.549540258803</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1627.344958227605</v>
+        <v>1636.145691308763</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>1172.277984326794</v>
+        <v>1181.675092922694</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>1310.809363349465</v>
+        <v>1320.217841417656</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>1404.084272178461</v>
+        <v>1413.255207802415</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>1537.402235006568</v>
+        <v>1546.549540258803</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>1627.344958227605</v>
+        <v>1636.145691308763</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>90493.06961541572</v>
+        <v>91218.47196342688</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>111344.0345505115</v>
+        <v>112143.2185786265</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>134728.9544181315</v>
+        <v>135608.9518599762</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>162508.4636991528</v>
+        <v>163475.3638959133</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>197296.474011104</v>
+        <v>198363.4595920324</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>490.6530194148507</v>
+        <v>511.2876928197333</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>540.1091285766462</v>
+        <v>560.6045790788239</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>581.3412681017219</v>
+        <v>602.6384447917933</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>678.1054185397649</v>
+        <v>699.457347858397</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>725.9370297288793</v>
+        <v>742.9393685104037</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>490.6530194148507</v>
+        <v>511.2876928197333</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>540.1091285766462</v>
+        <v>560.6045790788239</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>581.3412681017219</v>
+        <v>602.6384447917933</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>678.1054185397649</v>
+        <v>699.457347858397</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>725.9370297288793</v>
+        <v>742.9393685104037</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>8222822.995881463</v>
+        <v>8568638.185582172</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>9947157.719984176</v>
+        <v>10324621.21374988</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>11664102.01864643</v>
+        <v>12091411.1660484</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>13612802.59091012</v>
+        <v>14041437.41788955</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>15984621.49988644</v>
+        <v>16359001.01065063</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>506.0641955564727</v>
+        <v>527.3469941616174</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>556.6478766619387</v>
+        <v>577.7709208758602</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>598.9111043405458</v>
+        <v>620.851944103111</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>695.9037574834082</v>
+        <v>717.8161142292861</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>745.041018558989</v>
+        <v>762.490796273735</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>506.0641955564727</v>
+        <v>527.3469941616174</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>556.6478766619387</v>
+        <v>577.7709208758602</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>598.9111043405458</v>
+        <v>620.851944103111</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>695.9037574834082</v>
+        <v>717.8161142292861</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>745.041018558989</v>
+        <v>762.490796273735</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>8222822.995881463</v>
+        <v>8568638.185582172</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>9947157.719984176</v>
+        <v>10324621.21374988</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>11664102.01864643</v>
+        <v>12091411.1660484</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>13612802.59091012</v>
+        <v>14041437.41788955</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>15984621.49988644</v>
+        <v>16359001.01065063</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>2426.569050717375</v>
+        <v>2427.248800364531</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>2552.346064419263</v>
+        <v>2552.93336683514</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>2682.726579747776</v>
+        <v>2683.243829177098</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>2831.134549650115</v>
+        <v>2831.585170167327</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>2990.089602021656</v>
+        <v>2990.48006466449</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>2426.569050717375</v>
+        <v>2427.248800364531</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>2552.346064419263</v>
+        <v>2552.93336683514</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>2682.726579747776</v>
+        <v>2683.243829177098</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>2831.134549650115</v>
+        <v>2831.585170167327</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>2990.089602021656</v>
+        <v>2990.48006466449</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>3096781.174902076</v>
+        <v>3097648.669651643</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>3700082.225650087</v>
+        <v>3700933.625568131</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>4374951.674573725</v>
+        <v>4375795.19745603</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>5209968.64323729</v>
+        <v>5210797.893392485</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>6246890.791323044</v>
+        <v>6247706.545301196</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>1290.432062667656</v>
+        <v>1290.793548667413</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>1357.319378806268</v>
+        <v>1357.631702029754</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>1426.654804178691</v>
+        <v>1426.929873725051</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>1505.577100933765</v>
+        <v>1505.816737701297</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>1590.108260697223</v>
+        <v>1590.315905937501</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>1290.432062667656</v>
+        <v>1290.793548667413</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>1357.319378806268</v>
+        <v>1357.631702029754</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>1426.654804178691</v>
+        <v>1426.929873725051</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>1505.577100933765</v>
+        <v>1505.816737701297</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>1590.108260697223</v>
+        <v>1590.315905937501</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>3096781.174902076</v>
+        <v>3097648.669651643</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>3700082.225650087</v>
+        <v>3700933.625568131</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>4374951.674573725</v>
+        <v>4375795.19745603</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>5209968.64323729</v>
+        <v>5210797.893392485</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>6246890.791323044</v>
+        <v>6247706.545301196</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>627.6417997140932</v>
+        <v>646.8644280600296</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>686.9432402297329</v>
+        <v>705.985981467489</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>739.30040089344</v>
+        <v>759.0355702394075</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>858.8990162319906</v>
+        <v>878.4958263280897</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>922.1444054643824</v>
+        <v>937.7071890396448</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>627.6417997140932</v>
+        <v>646.8644280600296</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>686.9432402297329</v>
+        <v>705.985981467489</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>739.30040089344</v>
+        <v>759.0355702394075</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>858.8990162319906</v>
+        <v>878.4958263280897</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>922.1444054643824</v>
+        <v>937.7071890396448</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>11319604.17078354</v>
+        <v>11666286.85523382</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>13647239.94563426</v>
+        <v>14025554.83931801</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>16039053.69322015</v>
+        <v>16467206.36350444</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>18822771.23414741</v>
+        <v>19252235.31128203</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>22231512.29120948</v>
+        <v>22606707.55595183</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>607.0020542166095</v>
+        <v>625.5925542418485</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>662.6234197898358</v>
+        <v>680.9919917215065</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>711.5156604731008</v>
+        <v>730.5091332681583</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>817.6072758964914</v>
+        <v>836.2619654654975</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>875.8328818013441</v>
+        <v>890.61407822438</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>607.0020542166095</v>
+        <v>625.5925542418485</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>662.6234197898358</v>
+        <v>680.9919917215065</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>711.5156604731008</v>
+        <v>730.5091332681583</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>817.6072758964914</v>
+        <v>836.2619654654975</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>875.8328818013441</v>
+        <v>890.61407822438</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>11319604.17078354</v>
+        <v>11666286.85523382</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>13647239.94563426</v>
+        <v>14025554.83931801</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>16039053.69322015</v>
+        <v>16467206.36350444</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>18822771.23414741</v>
+        <v>19252235.31128203</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>22231512.29120948</v>
+        <v>22606707.55595183</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.3146440548149474</v>
+        <v>0.2993188257446636</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.1969582933994463</v>
+        <v>0.1875381125442844</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.1400214657993071</v>
+        <v>0.1328816196537178</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.09699586531249102</v>
+        <v>0.09241680647937342</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>0.05181273658821455</v>
+        <v>0.04991377355825399</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.3146440548149474</v>
+        <v>0.2993188257446636</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.1969582933994463</v>
+        <v>0.1875381125442844</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.1400214657993071</v>
+        <v>0.1328816196537178</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.09699586531249102</v>
+        <v>0.09241680647937342</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>0.05181273658821455</v>
+        <v>0.04991377355825399</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>4352.346691058558</v>
+        <v>4140.358862230859</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>3007.862467254741</v>
+        <v>2864.001511008901</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>2334.622199141255</v>
+        <v>2215.577285457539</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>1655.10493029917</v>
+        <v>1576.969405383688</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>969.1271590179581</v>
+        <v>933.6081579481628</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,49 +6384,49 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.3138395885571764</v>
+        <v>0.2985535422697578</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.1964547202385893</v>
+        <v>0.1870586244329432</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.1396634658851964</v>
+        <v>0.1325418745428424</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.09674787111208225</v>
+        <v>0.09218051978866401</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>0.05168026436231309</v>
+        <v>0.04978615650650561</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.3138395885571764</v>
+        <v>0.2985535422697578</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.1964547202385893</v>
+        <v>0.1870586244329432</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.1396634658851964</v>
+        <v>0.1325418745428424</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.09674787111208225</v>
+        <v>0.09218051978866401</v>
       </c>
       <c r="AC57" s="150" t="n">
-        <v>0.05168026436231309</v>
+        <v>0.04978615650650561</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>4352.346691058558</v>
+        <v>4140.358862230859</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>3007.862467254741</v>
+        <v>2864.001511008901</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>2334.622199141255</v>
+        <v>2215.577285457539</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>1655.10493029917</v>
+        <v>1576.969405383688</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>969.1271590179581</v>
+        <v>933.6081579481628</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6436,49 +6436,49 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>0.3115754436703133</v>
+        <v>0.3028245146066885</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.140491150831717</v>
+        <v>0.1368231872636653</v>
       </c>
       <c r="E58" s="156" t="n">
-        <v>0.1015573505611832</v>
+        <v>0.09906662286346035</v>
       </c>
       <c r="F58" s="156" t="n">
-        <v>0.08141768103264782</v>
+        <v>0.07947223107330419</v>
       </c>
       <c r="G58" s="157" t="n">
-        <v>0.04349887486115507</v>
+        <v>0.04260503889563628</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>0.3115754436703133</v>
+        <v>0.3028245146066885</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>0.140491150831717</v>
+        <v>0.1368231872636653</v>
       </c>
       <c r="J58" s="156" t="n">
-        <v>0.1015573505611832</v>
+        <v>0.09906662286346035</v>
       </c>
       <c r="K58" s="156" t="n">
-        <v>0.08141768103264782</v>
+        <v>0.07947223107330419</v>
       </c>
       <c r="L58" s="157" t="n">
-        <v>0.04349887486115507</v>
+        <v>0.04260503889563628</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>887.0879937329343</v>
+        <v>862.1731801169926</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>429.6485596328102</v>
+        <v>418.4312320326775</v>
       </c>
       <c r="O58" s="159" t="n">
-        <v>334.3595724170734</v>
+        <v>326.1592930338862</v>
       </c>
       <c r="P58" s="159" t="n">
-        <v>236.3234559141055</v>
+        <v>230.6765810354696</v>
       </c>
       <c r="Q58" s="160" t="n">
-        <v>138.7806988819104</v>
+        <v>135.9289658111946</v>
       </c>
       <c r="S58" s="32" t="inlineStr">
         <is>
@@ -6486,49 +6486,49 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>0.3851342870941585</v>
+        <v>0.3743173793602587</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.1736592543405454</v>
+        <v>0.169125333062193</v>
       </c>
       <c r="V58" s="156" t="n">
-        <v>0.1255336985059055</v>
+        <v>0.1224549429245664</v>
       </c>
       <c r="W58" s="156" t="n">
-        <v>0.1006393192351444</v>
+        <v>0.09823457425799535</v>
       </c>
       <c r="X58" s="157" t="n">
-        <v>0.0537683841887607</v>
+        <v>0.05266352536771877</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>0.3851342870941585</v>
+        <v>0.3743173793602587</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>0.1736592543405454</v>
+        <v>0.169125333062193</v>
       </c>
       <c r="AA58" s="156" t="n">
-        <v>0.1255336985059055</v>
+        <v>0.1224549429245664</v>
       </c>
       <c r="AB58" s="156" t="n">
-        <v>0.1006393192351444</v>
+        <v>0.09823457425799535</v>
       </c>
       <c r="AC58" s="157" t="n">
-        <v>0.0537683841887607</v>
+        <v>0.05266352536771877</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>887.0879937329343</v>
+        <v>862.1731801169926</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>429.6485596328102</v>
+        <v>418.4312320326775</v>
       </c>
       <c r="AF58" s="159" t="n">
-        <v>334.3595724170734</v>
+        <v>326.1592930338862</v>
       </c>
       <c r="AG58" s="159" t="n">
-        <v>236.3234559141055</v>
+        <v>230.6765810354696</v>
       </c>
       <c r="AH58" s="160" t="n">
-        <v>138.7806988819104</v>
+        <v>135.9289658111946</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" thickTop="1">
@@ -6538,49 +6538,49 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.3141202652260626</v>
+        <v>0.2999172213188337</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.1875371541481165</v>
+        <v>0.1790766896448272</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.1336787547142618</v>
+        <v>0.1273055455999006</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.09473117939683988</v>
+        <v>0.09053498270071003</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>0.0506012695174459</v>
+        <v>0.04884877011419521</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.3141202652260626</v>
+        <v>0.2999172213188337</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.1875371541481165</v>
+        <v>0.1790766896448272</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.1336787547142618</v>
+        <v>0.1273055455999006</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.09473117939683988</v>
+        <v>0.09053498270071003</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>0.0506012695174459</v>
+        <v>0.04884877011419521</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>5239.434684791492</v>
+        <v>5002.532042347852</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>3437.511026887551</v>
+        <v>3282.432743041578</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>2668.981771558329</v>
+        <v>2541.736578491425</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>1891.428386213275</v>
+        <v>1807.645986419157</v>
       </c>
       <c r="Q59" s="166" t="n">
-        <v>1107.907857899869</v>
+        <v>1069.537123759357</v>
       </c>
       <c r="S59" s="42" t="inlineStr">
         <is>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.3239942301516885</v>
+        <v>0.3093447318990955</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.1932835849302448</v>
+        <v>0.1845638786043223</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.1377214868198834</v>
+        <v>0.1311555381998503</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.09721755447120005</v>
+        <v>0.09291122171491768</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>0.05193290106398935</v>
+        <v>0.05013428259074452</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.3239942301516885</v>
+        <v>0.3093447318990955</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.1932835849302448</v>
+        <v>0.1845638786043223</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.1377214868198834</v>
+        <v>0.1311555381998503</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.09721755447120005</v>
+        <v>0.09291122171491768</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>0.05193290106398935</v>
+        <v>0.05013428259074452</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>5239.434684791492</v>
+        <v>5002.532042347852</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>3437.511026887551</v>
+        <v>3282.432743041578</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>2668.981771558329</v>
+        <v>2541.736578491425</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>1891.428386213275</v>
+        <v>1807.645986419157</v>
       </c>
       <c r="AH59" s="166" t="n">
-        <v>1107.907857899869</v>
+        <v>1069.537123759357</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" thickBot="1">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="C60" s="155" t="n">
-        <v>0.382788901847193</v>
+        <v>0.3794310678768668</v>
       </c>
       <c r="D60" s="156" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="155" t="n">
-        <v>0.382788901847193</v>
+        <v>0.3794310678768668</v>
       </c>
       <c r="I60" s="156" t="n">
         <v>0</v>
@@ -6670,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="158" t="n">
-        <v>30.32747865321118</v>
+        <v>30.06144524010887</v>
       </c>
       <c r="N60" s="159" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="T60" s="155" t="n">
-        <v>0.3928724674319574</v>
+        <v>0.3894261801681864</v>
       </c>
       <c r="U60" s="156" t="n">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="Y60" s="155" t="n">
-        <v>0.3928724674319574</v>
+        <v>0.3894261801681864</v>
       </c>
       <c r="Z60" s="156" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="AD60" s="158" t="n">
-        <v>30.32747865321118</v>
+        <v>30.06144524010887</v>
       </c>
       <c r="AE60" s="159" t="n">
         <v>0</v>
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.3144448954315729</v>
+        <v>0.3002931221320604</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.1866494065410075</v>
+        <v>0.1782289914729991</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.1330226060383991</v>
+        <v>0.1266806791777537</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.09421923434984553</v>
+        <v>0.09004571468706916</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>0.05031531960783869</v>
+        <v>0.04857272365267784</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.3144448954315729</v>
+        <v>0.3002931221320604</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.1866494065410075</v>
+        <v>0.1782289914729991</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.1330226060383991</v>
+        <v>0.1266806791777537</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.09421923434984553</v>
+        <v>0.09004571468706916</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>0.05031531960783869</v>
+        <v>0.04857272365267784</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>5269.762163444703</v>
+        <v>5032.59348758796</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>3437.511026887551</v>
+        <v>3282.432743041578</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>2668.981771558329</v>
+        <v>2541.736578491425</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>1891.428386213275</v>
+        <v>1807.645986419157</v>
       </c>
       <c r="Q61" s="166" t="n">
-        <v>1107.907857899869</v>
+        <v>1069.537123759357</v>
       </c>
       <c r="S61" s="42" t="inlineStr">
         <is>
@@ -6792,49 +6792,49 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.3243214588655636</v>
+        <v>0.3097251851504719</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.1923648209854664</v>
+        <v>0.1836865633515485</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.1370429389003477</v>
+        <v>0.130509340430453</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.09669222132520437</v>
+        <v>0.09240915863930042</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>0.05163943349707029</v>
+        <v>0.04985097883474966</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.3243214588655636</v>
+        <v>0.3097251851504719</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.1923648209854664</v>
+        <v>0.1836865633515485</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.1370429389003477</v>
+        <v>0.130509340430453</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.09669222132520437</v>
+        <v>0.09240915863930042</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>0.05163943349707029</v>
+        <v>0.04985097883474966</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>5269.762163444703</v>
+        <v>5032.59348758796</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>3437.511026887551</v>
+        <v>3282.432743041578</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>2668.981771558329</v>
+        <v>2541.736578491425</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>1891.428386213275</v>
+        <v>1807.645986419157</v>
       </c>
       <c r="AH61" s="166" t="n">
-        <v>1107.907857899869</v>
+        <v>1069.537123759357</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" thickBot="1">
@@ -6946,49 +6946,49 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.2921942285637997</v>
+        <v>0.2790438593190216</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.1730294896654889</v>
+        <v>0.1652235172330559</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.1230234234158363</v>
+        <v>0.1171582131580834</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.08630748150647798</v>
+        <v>0.082484419542564</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>0.04595508481608607</v>
+        <v>0.04436349908148787</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.2921942285637997</v>
+        <v>0.2790438593190216</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.1730294896654889</v>
+        <v>0.1652235172330559</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.1230234234158363</v>
+        <v>0.1171582131580834</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.08630748150647798</v>
+        <v>0.082484419542564</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>0.04595508481608607</v>
+        <v>0.04436349908148787</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>5269.762163444703</v>
+        <v>5032.59348758796</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>3437.511026887551</v>
+        <v>3282.432743041578</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>2668.981771558329</v>
+        <v>2541.736578491425</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>1891.428386213275</v>
+        <v>1807.645986419157</v>
       </c>
       <c r="Q63" s="184" t="n">
-        <v>1107.907857899869</v>
+        <v>1069.537123759357</v>
       </c>
       <c r="S63" s="51" t="inlineStr">
         <is>
@@ -6996,49 +6996,49 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.2825855401110268</v>
+        <v>0.2698676154142916</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.1669037344749081</v>
+        <v>0.1593741165311691</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.1183998984169324</v>
+        <v>0.1127551172896459</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.08215823223732548</v>
+        <v>0.07851896473459623</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>0.04364714911178026</v>
+        <v>0.04213549528369565</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.2825855401110268</v>
+        <v>0.2698676154142916</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.1669037344749081</v>
+        <v>0.1593741165311691</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.1183998984169324</v>
+        <v>0.1127551172896459</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.08215823223732548</v>
+        <v>0.07851896473459623</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>0.04364714911178026</v>
+        <v>0.04213549528369565</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>5269.762163444703</v>
+        <v>5032.59348758796</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>3437.511026887551</v>
+        <v>3282.432743041578</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>2668.981771558329</v>
+        <v>2541.736578491425</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>1891.428386213275</v>
+        <v>1807.645986419157</v>
       </c>
       <c r="AH63" s="190" t="n">
-        <v>1107.907857899869</v>
+        <v>1069.537123759357</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" thickBot="1"/>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>2.555161381276752</v>
+        <v>2.430708263919617</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>3.133047844526058</v>
+        <v>2.983199484175707</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>3.590343883132827</v>
+        <v>3.407268361183442</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>1.775118127836059</v>
+        <v>1.691316923352674</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>1.784111356110194</v>
+        <v>1.718722771571375</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>2.555161381276752</v>
+        <v>2.430708263919617</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>3.133047844526058</v>
+        <v>2.983199484175707</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>3.590343883132827</v>
+        <v>3.407268361183442</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>1.775118127836059</v>
+        <v>1.691316923352674</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>1.784111356110194</v>
+        <v>1.718722771571375</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>35344.53619173285</v>
+        <v>33623.02547118287</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>47846.56110190378</v>
+        <v>45558.14129942617</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>59862.93947334462</v>
+        <v>56810.46337460833</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>30290.02067025778</v>
+        <v>28860.06500917254</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>33370.76718530321</v>
+        <v>32147.71167156055</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>2.548628471841657</v>
+        <v>2.42449355002026</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>3.125037423746343</v>
+        <v>2.975572188224951</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>3.581164270603762</v>
+        <v>3.398556827036213</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>1.770579594164282</v>
+        <v>1.68699264842927</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>1.77954982900001</v>
+        <v>1.714328426739386</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>2.548628471841657</v>
+        <v>2.42449355002026</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>3.125037423746343</v>
+        <v>2.975572188224951</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>3.581164270603762</v>
+        <v>3.398556827036213</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>1.770579594164282</v>
+        <v>1.68699264842927</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>1.77954982900001</v>
+        <v>1.714328426739386</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>35344.53619173285</v>
+        <v>33623.02547118287</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>47846.56110190378</v>
+        <v>45558.14129942617</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>59862.93947334462</v>
+        <v>56810.46337460833</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>30290.02067025778</v>
+        <v>28860.06500917254</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>33370.76718530321</v>
+        <v>32147.71167156055</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,49 +7399,49 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>10.63919364653762</v>
+        <v>10.34038053149144</v>
       </c>
       <c r="D69" s="156" t="n">
-        <v>13.8665582969543</v>
+        <v>13.50452815949449</v>
       </c>
       <c r="E69" s="156" t="n">
-        <v>16.66721077961255</v>
+        <v>16.25844190859364</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>3.884095473578154</v>
+        <v>3.791286230115062</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>4.184874492837191</v>
+        <v>4.098881663256662</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>10.63919364653762</v>
+        <v>10.34038053149144</v>
       </c>
       <c r="I69" s="156" t="n">
-        <v>13.8665582969543</v>
+        <v>13.50452815949449</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>16.66721077961255</v>
+        <v>16.25844190859364</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>3.884095473578154</v>
+        <v>3.791286230115062</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>4.184874492837191</v>
+        <v>4.098881663256662</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>30290.90109177455</v>
+        <v>29440.1487872769</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>42406.56272000441</v>
+        <v>41299.40596185678</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>54873.83669288546</v>
+        <v>53528.03765248069</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>11273.99913353282</v>
+        <v>11004.61045925731</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>13351.60527031627</v>
+        <v>13077.25001340188</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,49 +7449,49 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>13.15096662319661</v>
+        <v>12.78160768180499</v>
       </c>
       <c r="U69" s="156" t="n">
-        <v>17.14026940389436</v>
+        <v>16.69276873678557</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>20.60211891488598</v>
+        <v>20.09684511708074</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>4.80107906964909</v>
+        <v>4.686358790682792</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>5.172868039250249</v>
+        <v>5.066573439375585</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>13.15096662319661</v>
+        <v>12.78160768180499</v>
       </c>
       <c r="Z69" s="156" t="n">
-        <v>17.14026940389436</v>
+        <v>16.69276873678557</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>20.60211891488598</v>
+        <v>20.09684511708074</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>4.80107906964909</v>
+        <v>4.686358790682792</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>5.172868039250249</v>
+        <v>5.066573439375585</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>30290.90109177455</v>
+        <v>29440.1487872769</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>42406.56272000441</v>
+        <v>41299.40596185678</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>54873.83669288546</v>
+        <v>53528.03765248069</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>11273.99913353282</v>
+        <v>11004.61045925731</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>13351.60527031627</v>
+        <v>13077.25001340188</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>3.935046852968725</v>
+        <v>3.780831753006789</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>4.923857367190323</v>
+        <v>4.73860799347463</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>5.746711918858616</v>
+        <v>5.526419689905779</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>2.081711708033294</v>
+        <v>1.996600955618102</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>2.133942226570042</v>
+        <v>2.065551262967732</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>3.935046852968725</v>
+        <v>3.780831753006789</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>4.923857367190323</v>
+        <v>4.73860799347463</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>5.746711918858616</v>
+        <v>5.526419689905779</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>2.081711708033294</v>
+        <v>1.996600955618102</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>2.133942226570042</v>
+        <v>2.065551262967732</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>65635.4372835074</v>
+        <v>63063.17425845978</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>90253.12382190819</v>
+        <v>86857.54726128295</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>114736.7761662301</v>
+        <v>110338.501027089</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>41564.01980379061</v>
+        <v>39864.67546842985</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>46722.37245561947</v>
+        <v>45224.96168496243</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>4.058739969612903</v>
+        <v>3.899677317115858</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>5.074732033440642</v>
+        <v>4.883806330102026</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>5.920504806335669</v>
+        <v>5.693550468145578</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>2.136349643883065</v>
+        <v>2.049005020268206</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>2.190099410263272</v>
+        <v>2.119908658523237</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>4.058739969612903</v>
+        <v>3.899677317115858</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>5.074732033440642</v>
+        <v>4.883806330102026</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>5.920504806335669</v>
+        <v>5.693550468145578</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>2.136349643883065</v>
+        <v>2.049005020268206</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>2.190099410263272</v>
+        <v>2.119908658523237</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>65635.4372835074</v>
+        <v>63063.17425845978</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>90253.12382190819</v>
+        <v>86857.54726128295</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>114736.7761662301</v>
+        <v>110338.501027089</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>41564.01980379061</v>
+        <v>39864.67546842985</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>46722.37245561947</v>
+        <v>45224.96168496243</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>7.85590233887873</v>
+        <v>7.786990164012222</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>9.493191150191411</v>
+        <v>9.412648489771547</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>10.77537937205628</v>
+        <v>10.68676903652186</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>9.162110620338812</v>
+        <v>9.088546274422864</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>9.732353498064473</v>
+        <v>9.656699521959773</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>7.85590233887873</v>
+        <v>7.786990164012222</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>9.493191150191411</v>
+        <v>9.412648489771547</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>10.77537937205628</v>
+        <v>10.68676903652186</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>9.162110620338812</v>
+        <v>9.088546274422864</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>9.732353498064473</v>
+        <v>9.656699521959773</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>622.4049582794967</v>
+        <v>616.9452061755951</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>827.6217610569504</v>
+        <v>820.600006474925</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>1061.188636549176</v>
+        <v>1052.462049957358</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>993.9768374021296</v>
+        <v>985.9960064638118</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>1211.015864900466</v>
+        <v>1201.602092032083</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>8.062845398302146</v>
+        <v>7.992117913661761</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>9.743264271720607</v>
+        <v>9.660599927012624</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>11.05922836578239</v>
+        <v>10.96828382430433</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>9.403462297174871</v>
+        <v>9.327960092289752</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>9.988726721839443</v>
+        <v>9.911079840961071</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>8.062845398302146</v>
+        <v>7.992117913661761</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>9.743264271720607</v>
+        <v>9.660599927012624</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>11.05922836578239</v>
+        <v>10.96828382430433</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>9.403462297174871</v>
+        <v>9.327960092289752</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>9.988726721839443</v>
+        <v>9.911079840961071</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>622.4049582794967</v>
+        <v>616.9452061755951</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>827.6217610569504</v>
+        <v>820.600006474925</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>1061.188636549176</v>
+        <v>1052.462049957358</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>993.9768374021296</v>
+        <v>985.9960064638118</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>1211.015864900466</v>
+        <v>1201.602092032083</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>3.953582653077728</v>
+        <v>3.799770821732543</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>4.945487295139095</v>
+        <v>4.760733573256229</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>5.771394625529713</v>
+        <v>5.551748743860604</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>2.119975510690225</v>
+        <v>2.034927157219664</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>2.176881169346826</v>
+        <v>2.108449162154338</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>3.953582653077728</v>
+        <v>3.799770821732543</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>4.945487295139095</v>
+        <v>4.760733573256229</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>5.771394625529713</v>
+        <v>5.551748743860604</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>2.119975510690225</v>
+        <v>2.034927157219664</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>2.176881169346826</v>
+        <v>2.108449162154338</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>66257.8422417869</v>
+        <v>63680.11946463538</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>91080.74558296513</v>
+        <v>87678.14726775787</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>115797.9648027793</v>
+        <v>111390.9630770464</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>42557.99664119274</v>
+        <v>40850.67147489366</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>47933.38832051994</v>
+        <v>46426.56377699451</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>4.077762789031453</v>
+        <v>3.919119801794568</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>5.096923670134029</v>
+        <v>4.906512581799881</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>5.945823079183621</v>
+        <v>5.719538855488563</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>2.175618839382009</v>
+        <v>2.088338208480414</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>2.234168663772079</v>
+        <v>2.163935778201041</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>4.077762789031453</v>
+        <v>3.919119801794568</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>5.096923670134029</v>
+        <v>4.906512581799881</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>5.945823079183621</v>
+        <v>5.719538855488563</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>2.175618839382009</v>
+        <v>2.088338208480414</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>2.234168663772079</v>
+        <v>2.163935778201041</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>66257.8422417869</v>
+        <v>63680.11946463538</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>91080.74558296513</v>
+        <v>87678.14726775787</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>115797.9648027793</v>
+        <v>111390.9630770464</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>42557.99664119274</v>
+        <v>40850.67147489366</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>47933.38832051994</v>
+        <v>46426.56377699451</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>21.26525340015822</v>
+        <v>21.26207295196642</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>26.64197220776437</v>
+        <v>26.63861966569218</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>33.52184395119496</v>
+        <v>33.51823510568492</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>41.67729024623739</v>
+        <v>41.6735024097534</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>50.90141856033816</v>
+        <v>50.8975305084747</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>21.26525340015822</v>
+        <v>21.26207295196642</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>26.64197220776437</v>
+        <v>26.63861966569218</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>33.52184395119496</v>
+        <v>33.51823510568492</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>41.67729024623739</v>
+        <v>41.6735024097534</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>50.90141856033816</v>
+        <v>50.8975305084747</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>27138.66163819395</v>
+        <v>27134.60275840019</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>38622.30486548145</v>
+        <v>38617.44475599044</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>54666.93789676762</v>
+        <v>54661.05264374683</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>76696.24015037752</v>
+        <v>76689.26962002608</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>106343.1686645334</v>
+        <v>106335.0457523084</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>11.30870963684465</v>
+        <v>11.30701829724764</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>14.16801023627824</v>
+        <v>14.16622737838672</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>17.82667681415264</v>
+        <v>17.82475765592633</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>22.1636848137295</v>
+        <v>22.16167046938367</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>27.06901026620621</v>
+        <v>27.06694262803847</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>11.30870963684465</v>
+        <v>11.30701829724764</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>14.16801023627824</v>
+        <v>14.16622737838672</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>17.82667681415264</v>
+        <v>17.82475765592633</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>22.1636848137295</v>
+        <v>22.16167046938367</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>27.06901026620621</v>
+        <v>27.06694262803847</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>27138.66163819395</v>
+        <v>27134.60275840019</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>38622.30486548145</v>
+        <v>38617.44475599044</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>54666.93789676762</v>
+        <v>54661.05264374683</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>76696.24015037752</v>
+        <v>76689.26962002608</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>106343.1686645334</v>
+        <v>106335.0457523084</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>5.178586538700305</v>
+        <v>5.035433645614485</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>6.52869254865259</v>
+        <v>6.357175777456733</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>7.857369475439067</v>
+        <v>7.653962892052598</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>5.441671972082279</v>
+        <v>5.363447205438317</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>6.399261645116545</v>
+        <v>6.336422900608592</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>5.178586538700305</v>
+        <v>5.035433645614485</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>6.52869254865259</v>
+        <v>6.357175777456733</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>7.857369475439067</v>
+        <v>7.653962892052598</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>5.441671972082279</v>
+        <v>5.363447205438317</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>6.399261645116545</v>
+        <v>6.336422900608592</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>93396.50387998085</v>
+        <v>90814.72222303557</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>129703.0504484466</v>
+        <v>126295.5920237483</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>170464.9026995469</v>
+        <v>166052.0157207932</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>119254.2367915703</v>
+        <v>117539.9410949197</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>154276.5569850533</v>
+        <v>152761.6095293029</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>5.008290825055742</v>
+        <v>4.869845456678866</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>6.297557541868878</v>
+        <v>6.132112971160091</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>7.56207006670354</v>
+        <v>7.366308006588466</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>5.180062514141656</v>
+        <v>5.105598418648812</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>6.077880790504577</v>
+        <v>6.01819790530238</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>5.008290825055742</v>
+        <v>4.869845456678866</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>6.297557541868878</v>
+        <v>6.132112971160091</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>7.56207006670354</v>
+        <v>7.366308006588466</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>5.180062514141656</v>
+        <v>5.105598418648812</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>6.077880790504577</v>
+        <v>6.01819790530238</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>93396.50387998085</v>
+        <v>90814.72222303557</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>129703.0504484466</v>
+        <v>126295.5920237483</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>170464.9026995469</v>
+        <v>166052.0157207932</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>119254.2367915703</v>
+        <v>117539.9410949197</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>154276.5569850533</v>
+        <v>152761.6095293029</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>421.0039999652951</v>
+        <v>440.9977874774129</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>462.4771255086719</v>
+        <v>482.4207662176969</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>497.4923347691823</v>
+        <v>518.5831896033579</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>568.2988410882808</v>
+        <v>589.0811871462281</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>608.3664005904086</v>
+        <v>624.5803741937897</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>421.0039999652951</v>
+        <v>440.9977874774129</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>462.4771255086719</v>
+        <v>482.4207662176969</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>497.4923347691823</v>
+        <v>518.5831896033579</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>568.2988410882808</v>
+        <v>589.0811871462281</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>608.3664005904086</v>
+        <v>624.5803741937897</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>5823581.720776634</v>
+        <v>6100147.870965848</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>7062752.03634205</v>
+        <v>7367322.751866226</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>8294847.093798196</v>
+        <v>8646501.589154691</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>9697260.916619601</v>
+        <v>10051883.90300026</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>11379140.34790187</v>
+        <v>11682413.31144981</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>419.927597893888</v>
+        <v>439.8702662852965</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>461.294687014223</v>
+        <v>481.1873368153887</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>496.2203711305973</v>
+        <v>517.2573019169417</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>566.8458428987717</v>
+        <v>587.5750536887706</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>606.810959659149</v>
+        <v>622.9834781818804</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>419.927597893888</v>
+        <v>439.8702662852965</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>461.294687014223</v>
+        <v>481.1873368153887</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>496.2203711305973</v>
+        <v>517.2573019169417</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>566.8458428987717</v>
+        <v>587.5750536887706</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>606.810959659149</v>
+        <v>622.9834781818804</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>5823581.720776634</v>
+        <v>6100147.870965848</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>7062752.03634205</v>
+        <v>7367322.751866226</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>8294847.093798196</v>
+        <v>8646501.589154691</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>9697260.916619601</v>
+        <v>10051883.90300026</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>11379140.34790187</v>
+        <v>11682413.31144981</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,49 +8362,49 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>835.8044764048716</v>
+        <v>858.8856315513453</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>937.4017868567873</v>
+        <v>959.8147013596572</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1018.105457948085</v>
+        <v>1039.442714435912</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1307.958625897351</v>
+        <v>1332.509602407463</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1396.675752547503</v>
+        <v>1418.147307190336</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>835.8044764048716</v>
+        <v>858.8856315513453</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>937.4017868567873</v>
+        <v>959.8147013596572</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>1018.105457948085</v>
+        <v>1039.442714435912</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>1307.958625897351</v>
+        <v>1332.509602407463</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>1396.675752547502</v>
+        <v>1418.147307190337</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>2379623.077457712</v>
+        <v>2445337.548953705</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>2866752.283940409</v>
+        <v>2935295.223309352</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>3351931.728367887</v>
+        <v>3422180.86263932</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>3796488.658781371</v>
+        <v>3867750.472448222</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>4456014.958286982</v>
+        <v>4524518.738417503</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,49 +8412,49 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>1033.126864487128</v>
+        <v>1061.657175245677</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1158.709956885724</v>
+        <v>1186.414264218426</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1258.466697871117</v>
+        <v>1284.841398550931</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1616.750367100985</v>
+        <v>1647.097504617036</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1726.412434569956</v>
+        <v>1752.953139423838</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>1033.126864487128</v>
+        <v>1061.657175245677</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>1158.709956885724</v>
+        <v>1186.414264218426</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>1258.466697871117</v>
+        <v>1284.841398550931</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>1616.750367100985</v>
+        <v>1647.097504617036</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1726.412434569956</v>
+        <v>1752.953139423838</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>2379623.077457712</v>
+        <v>2445337.548953705</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>2866752.283940409</v>
+        <v>2935295.223309352</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>3351931.728367887</v>
+        <v>3422180.86263932</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>3796488.658781371</v>
+        <v>3867750.472448222</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>4456014.958286982</v>
+        <v>4524518.738417503</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>491.8074223550757</v>
+        <v>512.3282010523632</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>541.7149116793554</v>
+        <v>562.070533076682</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>583.3411475382845</v>
+        <v>604.4726338673045</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>675.8272325194998</v>
+        <v>697.1574450138041</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>723.236102881305</v>
+        <v>740.2161929429938</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>491.8074223550757</v>
+        <v>512.3282010523632</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>541.7149116793554</v>
+        <v>562.070533076682</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>583.3411475382845</v>
+        <v>604.4726338673045</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>675.8272325194998</v>
+        <v>697.1574450138041</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>723.236102881305</v>
+        <v>740.2161929429938</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>8203204.798234347</v>
+        <v>8545485.419919552</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>9929504.320282459</v>
+        <v>10302617.97517558</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>11646778.82216608</v>
+        <v>12068682.45179401</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>13493749.57540097</v>
+        <v>13919634.37544849</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>15835155.30618885</v>
+        <v>16206932.04986732</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>507.2667536242688</v>
+        <v>528.4325765021911</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>558.3139011316193</v>
+        <v>579.2932505039079</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>600.982634330438</v>
+        <v>622.7531821049691</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>693.5654259655148</v>
+        <v>715.4554848484562</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>742.2689061959302</v>
+        <v>759.695847172723</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>507.2667536242688</v>
+        <v>528.4325765021911</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>558.3139011316193</v>
+        <v>579.2932505039079</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>600.982634330438</v>
+        <v>622.7531821049691</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>693.5654259655148</v>
+        <v>715.4554848484562</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>742.2689061959302</v>
+        <v>759.695847172723</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>8203204.798234347</v>
+        <v>8545485.419919552</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>9929504.320282459</v>
+        <v>10302617.97517558</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>11646778.82216608</v>
+        <v>12068682.45179401</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>13493749.57540097</v>
+        <v>13919634.37544849</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>15835155.30618885</v>
+        <v>16206932.04986732</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,49 +8566,49 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>1150.428687941912</v>
+        <v>1159.512337927867</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>1286.658984944233</v>
+        <v>1295.745439939102</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1378.822064244911</v>
+        <v>1387.669005945771</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1507.104985269625</v>
+        <v>1515.943949091569</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1595.309458349266</v>
+        <v>1603.808655580239</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>1150.428687941912</v>
+        <v>1159.512337927867</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>1286.658984944233</v>
+        <v>1295.745439939102</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>1378.822064244911</v>
+        <v>1387.669005945772</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>1507.104985269625</v>
+        <v>1515.943949091569</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1595.309458349266</v>
+        <v>1603.808655580239</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>91145.80205234843</v>
+        <v>91865.47861484259</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>112171.6563115685</v>
+        <v>112963.8185851014</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>135790.1430546806</v>
+        <v>136661.4139099335</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>163502.4405365549</v>
+        <v>164461.3599023771</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>198507.4898760045</v>
+        <v>199565.0616840645</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8616,49 +8616,49 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1180.733702192528</v>
+        <v>1190.056637016524</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1320.552627621185</v>
+        <v>1329.878441344668</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1415.143500544243</v>
+        <v>1424.22349162672</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1546.805697303743</v>
+        <v>1555.877500351093</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1637.333684949444</v>
+        <v>1646.056771149724</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>1180.733702192528</v>
+        <v>1190.056637016524</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>1320.552627621185</v>
+        <v>1329.878441344668</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>1415.143500544243</v>
+        <v>1424.22349162672</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>1546.805697303743</v>
+        <v>1555.877500351093</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>1637.333684949444</v>
+        <v>1646.056771149724</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>91145.80205234843</v>
+        <v>91865.47861484259</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>112171.6563115685</v>
+        <v>112963.8185851014</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>135790.1430546806</v>
+        <v>136661.4139099335</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>163502.4405365549</v>
+        <v>164461.3599023771</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>198507.4898760045</v>
+        <v>199565.0616840645</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>494.9210469633601</v>
+        <v>515.3877567635978</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>545.2412652783262</v>
+        <v>565.5435416435531</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>587.24568533329</v>
+        <v>608.3168742148318</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>680.3196132848049</v>
+        <v>701.5823207303036</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>728.1642262178339</v>
+        <v>745.0963903962107</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>494.9210469633601</v>
+        <v>515.3877567635978</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>545.2412652783262</v>
+        <v>565.5435416435531</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>587.24568533329</v>
+        <v>608.3168742148318</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>680.3196132848049</v>
+        <v>701.5823207303036</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>728.1642262178339</v>
+        <v>745.0963903962107</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>8294350.600286696</v>
+        <v>8637350.898534395</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>10041675.97659403</v>
+        <v>10415581.79376068</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>11782568.96522076</v>
+        <v>12205343.86570394</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>13657252.01593753</v>
+        <v>14084095.73535086</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>16033662.79606486</v>
+        <v>16406497.11155138</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>510.4662798043698</v>
+        <v>531.5758391485624</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>561.9371651530581</v>
+        <v>582.8611200210116</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>604.9939703586298</v>
+        <v>626.7019922990302</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>698.1760685441152</v>
+        <v>719.9968615964058</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>747.326826656258</v>
+        <v>764.7045830307708</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>510.4662798043698</v>
+        <v>531.5758391485624</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>561.9371651530581</v>
+        <v>582.8611200210116</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>604.9939703586298</v>
+        <v>626.7019922990302</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>698.1760685441152</v>
+        <v>719.9968615964058</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>747.326826656258</v>
+        <v>764.7045830307708</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>8294350.600286696</v>
+        <v>8637350.898534395</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>10041675.97659403</v>
+        <v>10415581.79376068</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>11782568.96522076</v>
+        <v>12205343.86570394</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>13657252.01593753</v>
+        <v>14084095.73535086</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>16033662.79606486</v>
+        <v>16406497.11155138</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>2447.834304117534</v>
+        <v>2448.510873316497</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>2578.988036627028</v>
+        <v>2579.571986500832</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>2716.248423698971</v>
+        <v>2716.762064282783</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>2872.811839896353</v>
+        <v>2873.258672577081</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>3040.991020581994</v>
+        <v>3041.377595172965</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>2447.834304117534</v>
+        <v>2448.510873316497</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>2578.988036627027</v>
+        <v>2579.571986500832</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>2716.248423698971</v>
+        <v>2716.762064282783</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>2872.811839896352</v>
+        <v>2873.258672577081</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>3040.991020581994</v>
+        <v>3041.377595172965</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>3123919.83654027</v>
+        <v>3124783.272410044</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>3738704.530515568</v>
+        <v>3739551.070324122</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>4429618.612470493</v>
+        <v>4430456.250099777</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>5286664.883387667</v>
+        <v>5287487.163012511</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>6353233.959987578</v>
+        <v>6354041.591053504</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>1301.740772304501</v>
+        <v>1302.10056696466</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>1371.487389042547</v>
+        <v>1371.79792940814</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>1444.481480992844</v>
+        <v>1444.754631380978</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>1527.740785747495</v>
+        <v>1527.97840817068</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>1617.177270963429</v>
+        <v>1617.382848565539</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>1301.740772304501</v>
+        <v>1302.10056696466</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>1371.487389042547</v>
+        <v>1371.79792940814</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>1444.481480992844</v>
+        <v>1444.754631380978</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>1527.740785747495</v>
+        <v>1527.97840817068</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>1617.177270963429</v>
+        <v>1617.382848565539</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>3123919.83654027</v>
+        <v>3124783.272410044</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>3738704.530515568</v>
+        <v>3739551.070324122</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>4429618.612470493</v>
+        <v>4430456.250099777</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>5286664.883387667</v>
+        <v>5287487.163012511</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>6353233.959987578</v>
+        <v>6354041.591053504</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>633.1125804813573</v>
+        <v>652.1789055649631</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>693.6449622680509</v>
+        <v>712.5083807621788</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>747.280793792295</v>
+        <v>766.8066913446183</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>864.4269956855791</v>
+        <v>883.9417579530707</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>928.589622194315</v>
+        <v>944.0879754393349</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>633.1125804813573</v>
+        <v>652.1789055649631</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>693.6449622680509</v>
+        <v>712.5083807621788</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>747.280793792295</v>
+        <v>766.8066913446183</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>864.4269956855791</v>
+        <v>883.9417579530707</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>928.589622194315</v>
+        <v>944.0879754393349</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>11418270.43682697</v>
+        <v>11762134.17094444</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>13780380.5071096</v>
+        <v>14155132.8640848</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>16212187.57769126</v>
+        <v>16635800.11580372</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>18943916.89932519</v>
+        <v>19371582.89836337</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>22386896.75605243</v>
+        <v>22760538.70260489</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>612.2929305817763</v>
+        <v>630.7322673139414</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>669.0878810661795</v>
+        <v>687.2834788091977</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>719.1961304382213</v>
+        <v>737.9881963920366</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>822.8694966428701</v>
+        <v>841.4460828488809</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>881.9544097409605</v>
+        <v>896.6744116249661</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>612.2929305817763</v>
+        <v>630.7322673139414</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>669.0878810661795</v>
+        <v>687.2834788091977</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>719.1961304382213</v>
+        <v>737.9881963920366</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>822.8694966428701</v>
+        <v>841.4460828488809</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>881.9544097409605</v>
+        <v>896.6744116249661</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>11418270.43682697</v>
+        <v>11762134.17094444</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>13780380.5071096</v>
+        <v>14155132.8640848</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>16212187.57769126</v>
+        <v>16635800.11580372</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>18943916.89932519</v>
+        <v>19371582.89836337</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>22386896.75605243</v>
+        <v>22760538.70260489</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9874,7 +9874,7 @@
         <v>1449.67889630279</v>
       </c>
       <c r="E95" s="80" t="n">
-        <v>1630.78552529384</v>
+        <v>1630.785525293841</v>
       </c>
       <c r="F95" s="80" t="n">
         <v>1840.240564999343</v>
@@ -9904,7 +9904,7 @@
         <v>1449.67889630279</v>
       </c>
       <c r="O95" s="80" t="n">
-        <v>1630.78552529384</v>
+        <v>1630.785525293841</v>
       </c>
       <c r="P95" s="80" t="n">
         <v>1840.240564999343</v>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="T95" s="79" t="n">
-        <v>2399.801790805035</v>
+        <v>2399.801790805036</v>
       </c>
       <c r="U95" s="80" t="n">
         <v>2726.021806970903</v>
@@ -9948,7 +9948,7 @@
         <v>0</v>
       </c>
       <c r="AD95" s="79" t="n">
-        <v>2399.801790805035</v>
+        <v>2399.801790805036</v>
       </c>
       <c r="AE95" s="80" t="n">
         <v>2726.021806970903</v>
@@ -9994,7 +9994,7 @@
         <v>19866.6194619955</v>
       </c>
       <c r="E96" s="133" t="n">
-        <v>21694.90733920481</v>
+        <v>21694.90733920482</v>
       </c>
       <c r="F96" s="133" t="n">
         <v>21914.99917734606</v>
@@ -10024,7 +10024,7 @@
         <v>19866.6194619955</v>
       </c>
       <c r="O96" s="133" t="n">
-        <v>21694.90733920481</v>
+        <v>21694.90733920482</v>
       </c>
       <c r="P96" s="133" t="n">
         <v>21914.99917734606</v>
